--- a/data/trans_camb/IP16B98-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Estudios-trans_camb.xlsx
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,84</t>
+          <t>0,0; 30,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 14,55</t>
+          <t>-8,44; 14,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 13,14</t>
+          <t>-4,07; 13,14</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,62</t>
+          <t>0,0; 43,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 17,21</t>
+          <t>-8,49; 17,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 15,1</t>
+          <t>-4,21; 15,13</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 51,01</t>
+          <t>-35,67; 55,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 55,22</t>
+          <t>-33,49; 55,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 44,31</t>
+          <t>-26,0; 40,33</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 150,5</t>
+          <t>-44,76; 188,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 123,38</t>
+          <t>-36,17; 124,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 82,3</t>
+          <t>-28,23; 81,61</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 19,86</t>
+          <t>-3,8; 19,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 16,6</t>
+          <t>-10,27; 16,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 12,75</t>
+          <t>-4,84; 12,24</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 25,59</t>
+          <t>-4,0; 25,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 19,74</t>
+          <t>-10,9; 19,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 15,21</t>
+          <t>-4,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B98-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Estudios-trans_camb.xlsx
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,43</t>
+          <t>0,0; 23,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 14,73</t>
+          <t>-8,34; 14,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 13,14</t>
+          <t>-2,33; 13,74</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,75</t>
+          <t>0,0; 31,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 17,28</t>
+          <t>-8,42; 17,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 15,13</t>
+          <t>-2,33; 16,13</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 55,44</t>
+          <t>-29,75; 56,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 55,46</t>
+          <t>-36,07; 55,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 40,33</t>
+          <t>-25,75; 42,02</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 188,3</t>
+          <t>-30,86; 193,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 124,53</t>
+          <t>-40,29; 124,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 81,61</t>
+          <t>-28,09; 83,08</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 19,37</t>
+          <t>-2,67; 19,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 16,64</t>
+          <t>-10,52; 15,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 12,24</t>
+          <t>-5,36; 12,75</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 25,06</t>
+          <t>-2,67; 24,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 19,98</t>
+          <t>-11,2; 18,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 14,21</t>
+          <t>-5,57; 15,08</t>
         </is>
       </c>
     </row>
